--- a/docs/strategy/PB-01_unit_economics_wezla.xlsx
+++ b/docs/strategy/PB-01_unit_economics_wezla.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="371">
   <si>
     <t xml:space="preserve">PB-01 — unit economics węzła vs cena 45 zł/mies. brutto</t>
   </si>
@@ -711,6 +711,27 @@
   </si>
   <si>
     <t xml:space="preserve">Jak S2, ale baza pakietu zmniejszona (patrz komórki poniżej).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uwaga po wdrożeniu Z-12 (2026-08-22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten arkusz liczy headroom tak, jak robił to kod PRZED poprawką: odejmuje rezerwę od pojemności</t>
+  </si>
+  <si>
+    <t xml:space="preserve">porównywanej z sumą limitów planów. Wdrożona wersja robi inaczej — headroom chroni REALNE zużycie,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a nie księgę handlową, bo „rezerwa pod burst” zabezpiecza przed zdarzeniem fizycznym.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Praktyczna różnica: w scenariuszu S2 arkusz podaje 51 kont, a kod wpuszcza 64. Model jest więc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zachowawczy wobec implementacji, nie z nią sprzeczny — decyzja cenowa oparta na 51 kontach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obowiązuje tym bardziej. Arkusz zostaje przy wersji ostrożniejszej celowo.</t>
   </si>
   <si>
     <t xml:space="preserve">Który zasób ogranicza (wybrany węzeł, scenariusz S2)</t>
@@ -3352,7 +3373,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3588,178 +3609,216 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B19" s="11" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="11" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D19" s="11" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+    <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B20" s="47" t="n">
+      <c r="B29" s="47" t="n">
         <f aca="false">Wezel!$B$31*(1-G15)</f>
         <v>102.4</v>
       </c>
-      <c r="C20" s="50" t="n">
+      <c r="C29" s="50" t="n">
         <f aca="false">H15/B15</f>
         <v>2</v>
       </c>
-      <c r="D20" s="36" t="n">
-        <f aca="false">FLOOR(B20/C20,1)</f>
+      <c r="D29" s="36" t="n">
+        <f aca="false">FLOOR(B29/C29,1)</f>
         <v>51</v>
       </c>
-      <c r="F20" s="29" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B21" s="47" t="n">
+      <c r="F29" s="29" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="47" t="n">
         <f aca="false">Wezel!$B$30*(1-G15)</f>
         <v>25.6</v>
       </c>
-      <c r="C21" s="50" t="n">
+      <c r="C30" s="50" t="n">
         <f aca="false">I15/C15</f>
         <v>0.5</v>
       </c>
-      <c r="D21" s="36" t="n">
-        <f aca="false">FLOOR(B21/C21,1)</f>
+      <c r="D30" s="36" t="n">
+        <f aca="false">FLOOR(B30/C30,1)</f>
         <v>51</v>
       </c>
-      <c r="F21" s="29" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B22" s="47" t="n">
+      <c r="F30" s="29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B31" s="47" t="n">
         <f aca="false">Wezel!$B$32*(1-G15)</f>
         <v>1536</v>
       </c>
-      <c r="C22" s="50" t="n">
+      <c r="C31" s="50" t="n">
         <f aca="false">J15/D15</f>
         <v>25</v>
       </c>
-      <c r="D22" s="36" t="n">
-        <f aca="false">FLOOR(B22/C22,1)</f>
+      <c r="D31" s="36" t="n">
+        <f aca="false">FLOOR(B31/C31,1)</f>
         <v>61</v>
       </c>
-      <c r="F22" s="51" t="s">
+      <c r="F31" s="51" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+      <c r="D34" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="52" t="n">
+      <c r="B35" s="52" t="n">
         <f aca="false">E15*Zalozenia!$B$30</f>
         <v>25.5</v>
       </c>
-      <c r="C26" s="47" t="n">
+      <c r="C35" s="47" t="n">
         <f aca="false">Wezel!$B$31</f>
         <v>128</v>
       </c>
-      <c r="D26" s="53" t="n">
-        <f aca="false">B26/C26</f>
+      <c r="D35" s="53" t="n">
+        <f aca="false">B35/C35</f>
         <v>0.19921875</v>
       </c>
-      <c r="F26" s="54" t="str">
-        <f aca="false">IF(D26&gt;0.85,"PRZEKROCZONE — overcommit za agresywny",IF(D26&gt;0.6,"ciasno, ale mieści się","zapas jest"))</f>
+      <c r="F35" s="54" t="str">
+        <f aca="false">IF(D35&gt;0.85,"PRZEKROCZONE — overcommit za agresywny",IF(D35&gt;0.6,"ciasno, ale mieści się","zapas jest"))</f>
         <v>zapas jest</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B27" s="52" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B36" s="52" t="n">
         <f aca="false">E15*Zalozenia!$B$31</f>
         <v>4.08</v>
       </c>
-      <c r="C27" s="47" t="n">
+      <c r="C36" s="47" t="n">
         <f aca="false">Wezel!$B$30</f>
         <v>32</v>
       </c>
-      <c r="D27" s="53" t="n">
-        <f aca="false">B27/C27</f>
+      <c r="D36" s="53" t="n">
+        <f aca="false">B36/C36</f>
         <v>0.1275</v>
       </c>
-      <c r="F27" s="54" t="str">
-        <f aca="false">IF(D27&gt;0.85,"PRZEKROCZONE — overcommit za agresywny",IF(D27&gt;0.6,"ciasno, ale mieści się","zapas jest"))</f>
+      <c r="F36" s="54" t="str">
+        <f aca="false">IF(D36&gt;0.85,"PRZEKROCZONE — overcommit za agresywny",IF(D36&gt;0.6,"ciasno, ale mieści się","zapas jest"))</f>
         <v>zapas jest</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B28" s="52" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B37" s="52" t="n">
         <f aca="false">E15*Zalozenia!$B$32</f>
         <v>408</v>
       </c>
-      <c r="C28" s="47" t="n">
+      <c r="C37" s="47" t="n">
         <f aca="false">Wezel!$B$32</f>
         <v>1920</v>
       </c>
-      <c r="D28" s="53" t="n">
-        <f aca="false">B28/C28</f>
+      <c r="D37" s="53" t="n">
+        <f aca="false">B37/C37</f>
         <v>0.2125</v>
       </c>
-      <c r="F28" s="54" t="str">
-        <f aca="false">IF(D28&gt;0.85,"PRZEKROCZONE — overcommit za agresywny",IF(D28&gt;0.6,"ciasno, ale mieści się","zapas jest"))</f>
+      <c r="F37" s="54" t="str">
+        <f aca="false">IF(D37&gt;0.85,"PRZEKROCZONE — overcommit za agresywny",IF(D37&gt;0.6,"ciasno, ale mieści się","zapas jest"))</f>
         <v>zapas jest</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>243</v>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3788,12 +3847,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3801,16 +3860,16 @@
         <v>40</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>116</v>
@@ -3837,12 +3896,12 @@
         <v>102</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B6" s="55" t="n">
         <f aca="false">B5*Zalozenia!$B$19</f>
@@ -3861,12 +3920,12 @@
         <v>3278.45414634146</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B7" s="55" t="n">
         <f aca="false">-Wezel!$B$29</f>
@@ -3885,12 +3944,12 @@
         <v>-1491.899905</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B8" s="55" t="n">
         <f aca="false">-B5*Zalozenia!$B$46</f>
@@ -3909,12 +3968,12 @@
         <v>-612</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="56" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B9" s="57" t="n">
         <f aca="false">SUM(B6:B8)</f>
@@ -3933,12 +3992,12 @@
         <v>1174.55424134146</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B10" s="40" t="n">
         <f aca="false">IF(B5=0,0,B9/B5)</f>
@@ -3957,12 +4016,12 @@
         <v>11.5152376602104</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B11" s="53" t="n">
         <f aca="false">IF(B6=0,0,B9/B6)</f>
@@ -3983,7 +4042,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4002,91 +4061,91 @@
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B15" s="55" t="n">
         <f aca="false">Zalozenia!$B$19-Zalozenia!$B$46</f>
         <v>26.1417073170732</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="58" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B16" s="59" t="n">
         <f aca="false">IF(B15&lt;=0,"cena nie pokrywa nawet wsparcia",CEILING(Wezel!$B$29/B15,1))</f>
         <v>58</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B17" s="60" t="n">
         <f aca="false">IF(ISNUMBER(B16),B16*Zalozenia!$B$23/Wezel!$B$31,"—")</f>
         <v>3.625</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B18" s="61" t="n">
         <f aca="false">IF(ISNUMBER(B16),B16*Zalozenia!$B$25/Wezel!$B$32,"—")</f>
         <v>1.51041666666667</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B19" s="53" t="n">
         <f aca="false">IF(ISNUMBER(B16),B16*Zalozenia!$B$32/Wezel!$B$32,"—")</f>
         <v>0.241666666666667</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="42" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">IF(C5=0,"—",(Wezel!$B$29/C5+Zalozenia!$B$46)/(1-Zalozenia!$B$15)*(1+Zalozenia!$B$8))</f>
         <v>163.404424324669</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B23" s="35" t="n">
         <f aca="false">IF(D5=0,"—",(Wezel!$B$29/D5+Zalozenia!$B$46)/(1-Zalozenia!$B$15)*(1+Zalozenia!$B$8))</f>
         <v>44.2009330844876</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -4115,22 +4174,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="62" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B5" s="63" t="n">
         <v>39</v>
@@ -4356,30 +4415,30 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>214</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4587,22 +4646,22 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -4633,12 +4692,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4649,13 +4708,13 @@
         <v>41</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4663,16 +4722,16 @@
         <v>44</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4680,50 +4739,50 @@
         <v>47</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="54" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="54" t="s">
+        <v>312</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="D8" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>299</v>
-      </c>
       <c r="E8" s="29" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4731,67 +4790,67 @@
         <v>124</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="54" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="54" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4799,271 +4858,271 @@
         <v>144</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="54" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="54" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="54" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B18" s="54" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="54" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="54" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>126</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="54" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B21" s="54" t="s">
         <v>126</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="54" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B22" s="54" t="s">
         <v>126</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="54" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B23" s="54" t="s">
         <v>126</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B24" s="54" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C24" s="37" t="s">
         <v>126</v>
       </c>
       <c r="D24" s="65" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="54" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B25" s="54" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C25" s="37" t="s">
         <v>126</v>
       </c>
       <c r="D25" s="65" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="54" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B26" s="54" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C26" s="37" t="s">
         <v>126</v>
       </c>
       <c r="D26" s="65" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="54" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B27" s="54" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C27" s="37" t="s">
         <v>126</v>
       </c>
       <c r="D27" s="65" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B28" s="54" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C28" s="37" t="s">
         <v>126</v>
       </c>
       <c r="D28" s="65" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
